--- a/public/templates/master_buku_induk_template.xlsx
+++ b/public/templates/master_buku_induk_template.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Template Master Buku Induk" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -15,9 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
-  <si>
-    <t>Nama Lengkap</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="120">
+  <si>
+    <t>Nomor</t>
+  </si>
+  <si>
+    <t>NIS</t>
   </si>
   <si>
     <t>NISN</t>
@@ -26,127 +29,352 @@
     <t>NIK</t>
   </si>
   <si>
-    <t>JK (L/P)</t>
-  </si>
-  <si>
-    <t>Tempat Lahir</t>
-  </si>
-  <si>
-    <t>Tanggal Lahir (YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>Angkatan (Thn Masuk)</t>
-  </si>
-  <si>
-    <t>Kelas / Rombel</t>
+    <t>Nama Lengkap Siswa</t>
+  </si>
+  <si>
+    <t>Nama Panggilan</t>
+  </si>
+  <si>
+    <t>Jenis Kelamin</t>
+  </si>
+  <si>
+    <t>Tempat Kelahiran</t>
+  </si>
+  <si>
+    <t>Tanggal Lahir</t>
   </si>
   <si>
     <t>Agama</t>
   </si>
   <si>
-    <t>Alamat Lengkap</t>
-  </si>
-  <si>
-    <t>No Induk</t>
-  </si>
-  <si>
-    <t>Nama Panggilan</t>
+    <t>Kewarganegaraan</t>
+  </si>
+  <si>
+    <t>Jumlah Saudara Kandung</t>
+  </si>
+  <si>
+    <t>Jumlah Saudara Tiri</t>
+  </si>
+  <si>
+    <t>Jumlah Saudara Angkat</t>
+  </si>
+  <si>
+    <t>Bahasa Sehari-hari</t>
+  </si>
+  <si>
+    <t>Berat Badan</t>
+  </si>
+  <si>
+    <t>Tinggi Badan</t>
+  </si>
+  <si>
+    <t>Golongan Darah</t>
+  </si>
+  <si>
+    <t>Nama Riwayat Penyakit</t>
+  </si>
+  <si>
+    <t>Kelainan Jasmani Siswa</t>
+  </si>
+  <si>
+    <t>Nomor Telepon</t>
+  </si>
+  <si>
+    <t>Alamat Tinggal</t>
+  </si>
+  <si>
+    <t>Bertempat Tinggal Pada</t>
+  </si>
+  <si>
+    <t>Jarak Tempat Tinggal ke Sekolah</t>
   </si>
   <si>
     <t>Nama Ayah</t>
   </si>
   <si>
+    <t>Pendidikan Terakhir Ayah</t>
+  </si>
+  <si>
+    <t>Pekerjaan Ayah</t>
+  </si>
+  <si>
     <t>Nama Ibu</t>
   </si>
   <si>
+    <t>Pendidikan Terakhir Ibu</t>
+  </si>
+  <si>
+    <t>Pekerjaan Ibu</t>
+  </si>
+  <si>
+    <t>Nama Wali</t>
+  </si>
+  <si>
+    <t>Status Hubungan Keluarga dengan Wali</t>
+  </si>
+  <si>
+    <t>Pendidikan Terakhir Wali</t>
+  </si>
+  <si>
+    <t>Pekerjaan Wali</t>
+  </si>
+  <si>
+    <t>Tingkat Siswa Saat Ini</t>
+  </si>
+  <si>
+    <t>0012345678</t>
+  </si>
+  <si>
+    <t>Ahmad Budi</t>
+  </si>
+  <si>
+    <t>Budi</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Jakarta</t>
+  </si>
+  <si>
+    <t>2010-05-12</t>
+  </si>
+  <si>
+    <t>Islam</t>
+  </si>
+  <si>
+    <t>WNI</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Tidak Ada</t>
+  </si>
+  <si>
+    <t>081234567890</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 1</t>
+  </si>
+  <si>
+    <t>Orang Tua</t>
+  </si>
+  <si>
+    <t>2 KM</t>
+  </si>
+  <si>
+    <t>Agus</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>Wiraswasta</t>
+  </si>
+  <si>
+    <t>Siti</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>Ibu Rumah Tangga</t>
+  </si>
+  <si>
+    <t>0012345679</t>
+  </si>
+  <si>
     <t>Budi Santoso</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Jakarta</t>
-  </si>
-  <si>
-    <t>2015-05-12</t>
-  </si>
-  <si>
-    <t>Kelas 4A</t>
-  </si>
-  <si>
-    <t>Islam</t>
-  </si>
-  <si>
-    <t>Jl. Merdeka No. 10, Jakarta Pusat</t>
-  </si>
-  <si>
-    <t>Budi</t>
-  </si>
-  <si>
-    <t>Slamet Santoso</t>
-  </si>
-  <si>
-    <t>Siti Aminah</t>
-  </si>
-  <si>
-    <t>Siti Rahmawati</t>
-  </si>
-  <si>
-    <t>0987654321</t>
+    <t>Toto</t>
+  </si>
+  <si>
+    <t>Bandung</t>
+  </si>
+  <si>
+    <t>2010-06-15</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Asma</t>
+  </si>
+  <si>
+    <t>081234567891</t>
+  </si>
+  <si>
+    <t>Jl. Sudirman No 5</t>
+  </si>
+  <si>
+    <t>5 KM</t>
+  </si>
+  <si>
+    <t>Santoso</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>PNS</t>
+  </si>
+  <si>
+    <t>Rina</t>
+  </si>
+  <si>
+    <t>Guru</t>
+  </si>
+  <si>
+    <t>0012345680</t>
+  </si>
+  <si>
+    <t>Citra Dewi</t>
+  </si>
+  <si>
+    <t>Citra</t>
   </si>
   <si>
     <t>P</t>
   </si>
   <si>
-    <t>Bandung</t>
-  </si>
-  <si>
-    <t>2016-02-20</t>
-  </si>
-  <si>
-    <t>Kelas 3B</t>
-  </si>
-  <si>
-    <t>Perum Kirana Blok C-12, Bandung</t>
-  </si>
-  <si>
-    <t>Siti</t>
-  </si>
-  <si>
-    <t>Mulyadi</t>
-  </si>
-  <si>
-    <t>Ratna</t>
-  </si>
-  <si>
-    <t>Agus Wijaya</t>
-  </si>
-  <si>
     <t>Surabaya</t>
   </si>
   <si>
-    <t>2014-11-30</t>
-  </si>
-  <si>
-    <t>Kelas 5C</t>
+    <t>2010-07-20</t>
   </si>
   <si>
     <t>Kristen</t>
   </si>
   <si>
-    <t>Jl. Pahlawan Gg. 3 No. 4, Surabaya</t>
-  </si>
-  <si>
-    <t>Agus</t>
-  </si>
-  <si>
-    <t>Herman Wijaya</t>
-  </si>
-  <si>
-    <t>Linda</t>
-  </si>
-  <si>
-    <t>Tingkat</t>
+    <t>B</t>
+  </si>
+  <si>
+    <t>081234567892</t>
+  </si>
+  <si>
+    <t>Jl. Pahlawan No 10</t>
+  </si>
+  <si>
+    <t>Asrama</t>
+  </si>
+  <si>
+    <t>10 KM</t>
+  </si>
+  <si>
+    <t>Haryo</t>
+  </si>
+  <si>
+    <t>Swasta</t>
+  </si>
+  <si>
+    <t>Maya</t>
+  </si>
+  <si>
+    <t>Joko</t>
+  </si>
+  <si>
+    <t>Paman</t>
+  </si>
+  <si>
+    <t>0012345681</t>
+  </si>
+  <si>
+    <t>Dewi Lestari</t>
+  </si>
+  <si>
+    <t>Dewi</t>
+  </si>
+  <si>
+    <t>Yogyakarta</t>
+  </si>
+  <si>
+    <t>2010-08-25</t>
+  </si>
+  <si>
+    <t>Katolik</t>
+  </si>
+  <si>
+    <t>Sunda</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>081234567893</t>
+  </si>
+  <si>
+    <t>Jl. Malioboro No 15</t>
+  </si>
+  <si>
+    <t>1 KM</t>
+  </si>
+  <si>
+    <t>Lestari</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>Dosen</t>
+  </si>
+  <si>
+    <t>Putri</t>
+  </si>
+  <si>
+    <t>Arsitek</t>
+  </si>
+  <si>
+    <t>0012345682</t>
+  </si>
+  <si>
+    <t>Eko Prasetyo</t>
+  </si>
+  <si>
+    <t>Eko</t>
+  </si>
+  <si>
+    <t>Semarang</t>
+  </si>
+  <si>
+    <t>2010-09-30</t>
+  </si>
+  <si>
+    <t>Hindu</t>
+  </si>
+  <si>
+    <t>Jawa</t>
+  </si>
+  <si>
+    <t>Mata Minus</t>
+  </si>
+  <si>
+    <t>081234567894</t>
+  </si>
+  <si>
+    <t>Jl. Pemuda No 20</t>
+  </si>
+  <si>
+    <t>3 KM</t>
+  </si>
+  <si>
+    <t>Prasetyo</t>
+  </si>
+  <si>
+    <t>Pengusaha</t>
+  </si>
+  <si>
+    <t>Nia</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Perawat</t>
   </si>
 </sst>
 </file>
@@ -154,7 +382,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -162,15 +390,6 @@
       <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -192,12 +411,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4F81BD"/>
+        <fgColor rgb="FFD3D3D3"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -205,32 +424,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,26 +730,47 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.567" customWidth="true" style="0"/>
-    <col min="2" max="2" width="12.854" customWidth="true" style="0"/>
-    <col min="3" max="3" width="19.995" customWidth="true" style="0"/>
-    <col min="4" max="4" width="12.854" customWidth="true" style="0"/>
-    <col min="5" max="5" width="17.567" customWidth="true" style="0"/>
-    <col min="6" max="6" width="33.992" customWidth="true" style="0"/>
-    <col min="7" max="7" width="26.993" customWidth="true" style="0"/>
-    <col min="8" max="8" width="19.852" customWidth="true" style="0"/>
-    <col min="9" max="9" width="9.283" customWidth="true" style="0"/>
-    <col min="10" max="10" width="41.133" customWidth="true" style="0"/>
-    <col min="11" max="11" width="12.854" customWidth="true" style="0"/>
-    <col min="12" max="12" width="19.852" customWidth="true" style="0"/>
-    <col min="13" max="13" width="17.567" customWidth="true" style="0"/>
-    <col min="14" max="14" width="13.997" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="22" max="22" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="23" max="23" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="24" max="24" width="37.705" bestFit="true" customWidth="true" style="0"/>
+    <col min="25" max="25" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="26" max="26" width="29.421" bestFit="true" customWidth="true" style="0"/>
+    <col min="27" max="27" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="28" max="28" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="29" max="29" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="30" max="30" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="31" max="31" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="32" max="32" width="43.561" bestFit="true" customWidth="true" style="0"/>
+    <col min="33" max="33" width="29.421" bestFit="true" customWidth="true" style="0"/>
+    <col min="34" max="34" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="35" max="35" width="26.993" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -592,140 +813,571 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2">
+        <v>1234567890123456</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
         <v>43</v>
       </c>
+      <c r="P2">
+        <v>45.5</v>
+      </c>
+      <c r="Q2">
+        <v>150.2</v>
+      </c>
+      <c r="R2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1234567890</v>
-      </c>
-      <c r="C2" s="2">
-        <v>3201020304050607</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="2">
-        <v>2021</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="2">
-        <v>2122.001</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>23</v>
+    <row r="3" spans="1:35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1002</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3">
+        <v>1234567890123457</v>
+      </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3">
+        <v>42.0</v>
+      </c>
+      <c r="Q3">
+        <v>148.5</v>
+      </c>
+      <c r="R3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" t="s">
+        <v>63</v>
+      </c>
+      <c r="V3" t="s">
+        <v>64</v>
+      </c>
+      <c r="W3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2">
-        <v>3201020304050608</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2">
-        <v>2022</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2">
-        <v>2223.005</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>33</v>
+    <row r="4" spans="1:35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1003</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4">
+        <v>1234567890123458</v>
+      </c>
+      <c r="E4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4">
+        <v>40.5</v>
+      </c>
+      <c r="Q4">
+        <v>145.0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S4" t="s">
+        <v>45</v>
+      </c>
+      <c r="T4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" t="s">
+        <v>80</v>
+      </c>
+      <c r="W4" t="s">
+        <v>81</v>
+      </c>
+      <c r="X4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI4">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1122334455</v>
-      </c>
-      <c r="C4" s="2">
-        <v>3201020304050609</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="2">
-        <v>2020</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="2" t="s">
+    <row r="5" spans="1:35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1004</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5">
+        <v>1234567890123459</v>
+      </c>
+      <c r="E5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>94</v>
+      </c>
+      <c r="P5">
+        <v>48.0</v>
+      </c>
+      <c r="Q5">
+        <v>155.0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>95</v>
+      </c>
+      <c r="S5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" t="s">
+        <v>96</v>
+      </c>
+      <c r="V5" t="s">
+        <v>97</v>
+      </c>
+      <c r="W5" t="s">
+        <v>48</v>
+      </c>
+      <c r="X5" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE5"/>
+      <c r="AF5"/>
+      <c r="AG5"/>
+      <c r="AH5"/>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1005</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6">
+        <v>1234567890123460</v>
+      </c>
+      <c r="E6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="2">
-        <v>2021.012</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" s="2" t="s">
+      <c r="H6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" t="s">
+        <v>108</v>
+      </c>
+      <c r="J6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K6" t="s">
         <v>42</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>110</v>
+      </c>
+      <c r="P6">
+        <v>50.0</v>
+      </c>
+      <c r="Q6">
+        <v>160.0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S6" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" t="s">
+        <v>111</v>
+      </c>
+      <c r="U6" t="s">
+        <v>112</v>
+      </c>
+      <c r="V6" t="s">
+        <v>113</v>
+      </c>
+      <c r="W6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X6" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE6"/>
+      <c r="AF6"/>
+      <c r="AG6"/>
+      <c r="AH6"/>
+      <c r="AI6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/master_buku_induk_template.xlsx
+++ b/public/templates/master_buku_induk_template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="271">
   <si>
     <t>Nomor</t>
   </si>
@@ -122,259 +122,712 @@
     <t>Tingkat Siswa Saat Ini</t>
   </si>
   <si>
-    <t>0012345678</t>
-  </si>
-  <si>
-    <t>Ahmad Budi</t>
+    <t>1000000001</t>
+  </si>
+  <si>
+    <t>3275578163665349</t>
+  </si>
+  <si>
+    <t>Putri Kurniawan</t>
+  </si>
+  <si>
+    <t>Putri</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Jakarta</t>
+  </si>
+  <si>
+    <t>2017-03-26</t>
+  </si>
+  <si>
+    <t>Islam</t>
+  </si>
+  <si>
+    <t>WNI</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Tidak Ada</t>
+  </si>
+  <si>
+    <t>081281803765</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 63</t>
+  </si>
+  <si>
+    <t>Orang Tua</t>
+  </si>
+  <si>
+    <t>6 KM</t>
+  </si>
+  <si>
+    <t>Cahyono Kurniawan</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Karyawan Swasta</t>
+  </si>
+  <si>
+    <t>Titik</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>Guru</t>
+  </si>
+  <si>
+    <t>1000000002</t>
+  </si>
+  <si>
+    <t>3275572157817432</t>
+  </si>
+  <si>
+    <t>Joko Pratama</t>
+  </si>
+  <si>
+    <t>Joko</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>2017-06-12</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>081283109100</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 61</t>
+  </si>
+  <si>
+    <t>4 KM</t>
+  </si>
+  <si>
+    <t>Cahyono Pratama</t>
+  </si>
+  <si>
+    <t>PNS</t>
+  </si>
+  <si>
+    <t>1000000003</t>
+  </si>
+  <si>
+    <t>3271609777251809</t>
+  </si>
+  <si>
+    <t>Siti Nugroho</t>
+  </si>
+  <si>
+    <t>Siti</t>
+  </si>
+  <si>
+    <t>2017-11-22</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>081270112677</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 81</t>
+  </si>
+  <si>
+    <t>2 KM</t>
+  </si>
+  <si>
+    <t>Bambang Nugroho</t>
+  </si>
+  <si>
+    <t>Sri</t>
+  </si>
+  <si>
+    <t>1000000004</t>
+  </si>
+  <si>
+    <t>3275503047188661</t>
+  </si>
+  <si>
+    <t>Deni Pratama</t>
+  </si>
+  <si>
+    <t>Deni</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>081254668254</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 83</t>
+  </si>
+  <si>
+    <t>3 KM</t>
+  </si>
+  <si>
+    <t>Deddy Pratama</t>
+  </si>
+  <si>
+    <t>Endang</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>1000000005</t>
+  </si>
+  <si>
+    <t>3277961608350302</t>
+  </si>
+  <si>
+    <t>2017-08-17</t>
+  </si>
+  <si>
+    <t>081288067701</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 12</t>
+  </si>
+  <si>
+    <t>Yuni</t>
+  </si>
+  <si>
+    <t>1000000006</t>
+  </si>
+  <si>
+    <t>3277581179046503</t>
+  </si>
+  <si>
+    <t>Iwan Nugroho</t>
+  </si>
+  <si>
+    <t>Iwan</t>
+  </si>
+  <si>
+    <t>2016-07-15</t>
+  </si>
+  <si>
+    <t>081217590653</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 88</t>
+  </si>
+  <si>
+    <t>10 KM</t>
+  </si>
+  <si>
+    <t>Agus Nugroho</t>
+  </si>
+  <si>
+    <t>1000000007</t>
+  </si>
+  <si>
+    <t>3274278580527347</t>
+  </si>
+  <si>
+    <t>Lestari Wijaya</t>
+  </si>
+  <si>
+    <t>Lestari</t>
+  </si>
+  <si>
+    <t>2016-12-08</t>
+  </si>
+  <si>
+    <t>081210117778</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 95</t>
+  </si>
+  <si>
+    <t>Cahyono Wijaya</t>
+  </si>
+  <si>
+    <t>1000000008</t>
+  </si>
+  <si>
+    <t>3274763082068942</t>
+  </si>
+  <si>
+    <t>Lestari Nugroho</t>
+  </si>
+  <si>
+    <t>2016-06-24</t>
+  </si>
+  <si>
+    <t>081249583563</t>
+  </si>
+  <si>
+    <t>9 KM</t>
+  </si>
+  <si>
+    <t>Wiraswasta</t>
+  </si>
+  <si>
+    <t>1000000009</t>
+  </si>
+  <si>
+    <t>3276680578070577</t>
+  </si>
+  <si>
+    <t>2016-07-04</t>
+  </si>
+  <si>
+    <t>081249782497</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 21</t>
+  </si>
+  <si>
+    <t>1000000010</t>
+  </si>
+  <si>
+    <t>3278686601696658</t>
+  </si>
+  <si>
+    <t>Sari Pratama</t>
+  </si>
+  <si>
+    <t>Sari</t>
+  </si>
+  <si>
+    <t>2016-06-13</t>
+  </si>
+  <si>
+    <t>081227376745</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 1</t>
+  </si>
+  <si>
+    <t>Bambang Pratama</t>
+  </si>
+  <si>
+    <t>1000000011</t>
+  </si>
+  <si>
+    <t>3277415525845429</t>
+  </si>
+  <si>
+    <t>Ayu Nugroho</t>
+  </si>
+  <si>
+    <t>Ayu</t>
+  </si>
+  <si>
+    <t>2015-10-02</t>
+  </si>
+  <si>
+    <t>081272186655</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 46</t>
+  </si>
+  <si>
+    <t>Cahyono Nugroho</t>
+  </si>
+  <si>
+    <t>1000000012</t>
+  </si>
+  <si>
+    <t>3276189271953402</t>
+  </si>
+  <si>
+    <t>Ayu Wibowo</t>
+  </si>
+  <si>
+    <t>2015-11-05</t>
+  </si>
+  <si>
+    <t>081295418093</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 74</t>
+  </si>
+  <si>
+    <t>Agus Wibowo</t>
+  </si>
+  <si>
+    <t>1000000013</t>
+  </si>
+  <si>
+    <t>3277107415959942</t>
+  </si>
+  <si>
+    <t>Budi Kurniawan</t>
   </si>
   <si>
     <t>Budi</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Jakarta</t>
-  </si>
-  <si>
-    <t>2010-05-12</t>
-  </si>
-  <si>
-    <t>Islam</t>
-  </si>
-  <si>
-    <t>WNI</t>
-  </si>
-  <si>
-    <t>Indonesia</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>Tidak Ada</t>
-  </si>
-  <si>
-    <t>081234567890</t>
-  </si>
-  <si>
-    <t>Jl. Merdeka No 1</t>
-  </si>
-  <si>
-    <t>Orang Tua</t>
-  </si>
-  <si>
-    <t>2 KM</t>
-  </si>
-  <si>
-    <t>Agus</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>Wiraswasta</t>
-  </si>
-  <si>
-    <t>Siti</t>
-  </si>
-  <si>
-    <t>SMA</t>
+    <t>2015-04-16</t>
+  </si>
+  <si>
+    <t>081271087472</t>
+  </si>
+  <si>
+    <t>8 KM</t>
+  </si>
+  <si>
+    <t>Agus Kurniawan</t>
+  </si>
+  <si>
+    <t>1000000014</t>
+  </si>
+  <si>
+    <t>3274316679464281</t>
+  </si>
+  <si>
+    <t>2015-09-06</t>
+  </si>
+  <si>
+    <t>081278920561</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 90</t>
   </si>
   <si>
     <t>Ibu Rumah Tangga</t>
   </si>
   <si>
-    <t>0012345679</t>
-  </si>
-  <si>
-    <t>Budi Santoso</t>
-  </si>
-  <si>
-    <t>Toto</t>
-  </si>
-  <si>
-    <t>Bandung</t>
-  </si>
-  <si>
-    <t>2010-06-15</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Asma</t>
-  </si>
-  <si>
-    <t>081234567891</t>
-  </si>
-  <si>
-    <t>Jl. Sudirman No 5</t>
+    <t>1000000015</t>
+  </si>
+  <si>
+    <t>3273385249932779</t>
+  </si>
+  <si>
+    <t>Siti Wijaya</t>
+  </si>
+  <si>
+    <t>2015-03-16</t>
+  </si>
+  <si>
+    <t>081230824608</t>
+  </si>
+  <si>
+    <t>1 KM</t>
+  </si>
+  <si>
+    <t>Agus Wijaya</t>
+  </si>
+  <si>
+    <t>1000000016</t>
+  </si>
+  <si>
+    <t>3272324070828470</t>
+  </si>
+  <si>
+    <t>Rina Wibowo</t>
+  </si>
+  <si>
+    <t>Rina</t>
+  </si>
+  <si>
+    <t>2014-02-13</t>
+  </si>
+  <si>
+    <t>Hindu</t>
+  </si>
+  <si>
+    <t>081274641269</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 35</t>
+  </si>
+  <si>
+    <t>7 KM</t>
+  </si>
+  <si>
+    <t>Cahyono Wibowo</t>
+  </si>
+  <si>
+    <t>1000000017</t>
+  </si>
+  <si>
+    <t>3276899804828826</t>
+  </si>
+  <si>
+    <t>Rina Wijaya</t>
+  </si>
+  <si>
+    <t>2014-11-26</t>
+  </si>
+  <si>
+    <t>Katolik</t>
+  </si>
+  <si>
+    <t>081210489861</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 5</t>
+  </si>
+  <si>
+    <t>Deddy Wijaya</t>
+  </si>
+  <si>
+    <t>1000000018</t>
+  </si>
+  <si>
+    <t>3276565281464489</t>
+  </si>
+  <si>
+    <t>Lestari Saputra</t>
+  </si>
+  <si>
+    <t>2014-05-09</t>
+  </si>
+  <si>
+    <t>Buddha</t>
+  </si>
+  <si>
+    <t>081212703983</t>
+  </si>
+  <si>
+    <t>Cahyono Saputra</t>
+  </si>
+  <si>
+    <t>1000000019</t>
+  </si>
+  <si>
+    <t>3272014659855126</t>
+  </si>
+  <si>
+    <t>2014-04-28</t>
+  </si>
+  <si>
+    <t>081234309064</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 14</t>
+  </si>
+  <si>
+    <t>1000000020</t>
+  </si>
+  <si>
+    <t>3277133173265291</t>
+  </si>
+  <si>
+    <t>Candra Nugroho</t>
+  </si>
+  <si>
+    <t>Candra</t>
+  </si>
+  <si>
+    <t>2014-10-05</t>
+  </si>
+  <si>
+    <t>Kristen</t>
+  </si>
+  <si>
+    <t>081294123259</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 82</t>
+  </si>
+  <si>
+    <t>1000000021</t>
+  </si>
+  <si>
+    <t>3278754876138103</t>
+  </si>
+  <si>
+    <t>Putri Nugroho</t>
+  </si>
+  <si>
+    <t>2013-12-05</t>
+  </si>
+  <si>
+    <t>081211577911</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 99</t>
+  </si>
+  <si>
+    <t>1000000022</t>
+  </si>
+  <si>
+    <t>3279847433642396</t>
+  </si>
+  <si>
+    <t>2013-01-16</t>
+  </si>
+  <si>
+    <t>081281330133</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 78</t>
+  </si>
+  <si>
+    <t>1000000023</t>
+  </si>
+  <si>
+    <t>3278140766124545</t>
+  </si>
+  <si>
+    <t>Ahmad Pratama</t>
+  </si>
+  <si>
+    <t>Ahmad</t>
+  </si>
+  <si>
+    <t>2013-02-14</t>
+  </si>
+  <si>
+    <t>081296468601</t>
+  </si>
+  <si>
+    <t>1000000024</t>
+  </si>
+  <si>
+    <t>3275354414713057</t>
+  </si>
+  <si>
+    <t>Candra Wijaya</t>
+  </si>
+  <si>
+    <t>2013-04-01</t>
+  </si>
+  <si>
+    <t>081299997113</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 84</t>
+  </si>
+  <si>
+    <t>Bambang Wijaya</t>
+  </si>
+  <si>
+    <t>1000000025</t>
+  </si>
+  <si>
+    <t>3272649752272543</t>
+  </si>
+  <si>
+    <t>Fitri Wibowo</t>
+  </si>
+  <si>
+    <t>Fitri</t>
+  </si>
+  <si>
+    <t>2013-01-25</t>
+  </si>
+  <si>
+    <t>081268174852</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 56</t>
+  </si>
+  <si>
+    <t>Bambang Wibowo</t>
+  </si>
+  <si>
+    <t>1000000026</t>
+  </si>
+  <si>
+    <t>3274406577921011</t>
+  </si>
+  <si>
+    <t>2012-02-15</t>
+  </si>
+  <si>
+    <t>081278314824</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 69</t>
+  </si>
+  <si>
+    <t>1000000027</t>
+  </si>
+  <si>
+    <t>3272219150040173</t>
+  </si>
+  <si>
+    <t>Lestari Wibowo</t>
+  </si>
+  <si>
+    <t>2012-01-22</t>
+  </si>
+  <si>
+    <t>081215386349</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 55</t>
   </si>
   <si>
     <t>5 KM</t>
   </si>
   <si>
-    <t>Santoso</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>PNS</t>
-  </si>
-  <si>
-    <t>Rina</t>
-  </si>
-  <si>
-    <t>Guru</t>
-  </si>
-  <si>
-    <t>0012345680</t>
-  </si>
-  <si>
-    <t>Citra Dewi</t>
-  </si>
-  <si>
-    <t>Citra</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Surabaya</t>
-  </si>
-  <si>
-    <t>2010-07-20</t>
-  </si>
-  <si>
-    <t>Kristen</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>081234567892</t>
-  </si>
-  <si>
-    <t>Jl. Pahlawan No 10</t>
-  </si>
-  <si>
-    <t>Asrama</t>
-  </si>
-  <si>
-    <t>10 KM</t>
-  </si>
-  <si>
-    <t>Haryo</t>
-  </si>
-  <si>
-    <t>Swasta</t>
-  </si>
-  <si>
-    <t>Maya</t>
-  </si>
-  <si>
-    <t>Joko</t>
-  </si>
-  <si>
-    <t>Paman</t>
-  </si>
-  <si>
-    <t>0012345681</t>
-  </si>
-  <si>
-    <t>Dewi Lestari</t>
-  </si>
-  <si>
-    <t>Dewi</t>
-  </si>
-  <si>
-    <t>Yogyakarta</t>
-  </si>
-  <si>
-    <t>2010-08-25</t>
-  </si>
-  <si>
-    <t>Katolik</t>
-  </si>
-  <si>
-    <t>Sunda</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>081234567893</t>
-  </si>
-  <si>
-    <t>Jl. Malioboro No 15</t>
-  </si>
-  <si>
-    <t>1 KM</t>
-  </si>
-  <si>
-    <t>Lestari</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>Dosen</t>
-  </si>
-  <si>
-    <t>Putri</t>
-  </si>
-  <si>
-    <t>Arsitek</t>
-  </si>
-  <si>
-    <t>0012345682</t>
-  </si>
-  <si>
-    <t>Eko Prasetyo</t>
-  </si>
-  <si>
-    <t>Eko</t>
-  </si>
-  <si>
-    <t>Semarang</t>
-  </si>
-  <si>
-    <t>2010-09-30</t>
-  </si>
-  <si>
-    <t>Hindu</t>
-  </si>
-  <si>
-    <t>Jawa</t>
-  </si>
-  <si>
-    <t>Mata Minus</t>
-  </si>
-  <si>
-    <t>081234567894</t>
-  </si>
-  <si>
-    <t>Jl. Pemuda No 20</t>
-  </si>
-  <si>
-    <t>3 KM</t>
-  </si>
-  <si>
-    <t>Prasetyo</t>
-  </si>
-  <si>
-    <t>Pengusaha</t>
-  </si>
-  <si>
-    <t>Nia</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>Perawat</t>
+    <t>Deddy Wibowo</t>
+  </si>
+  <si>
+    <t>1000000028</t>
+  </si>
+  <si>
+    <t>3275741009797622</t>
+  </si>
+  <si>
+    <t>Indah Kurniawan</t>
+  </si>
+  <si>
+    <t>Indah</t>
+  </si>
+  <si>
+    <t>2012-12-24</t>
+  </si>
+  <si>
+    <t>081274570548</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No 3</t>
+  </si>
+  <si>
+    <t>Deddy Kurniawan</t>
+  </si>
+  <si>
+    <t>1000000029</t>
+  </si>
+  <si>
+    <t>3272219902301031</t>
+  </si>
+  <si>
+    <t>Iwan Pratama</t>
+  </si>
+  <si>
+    <t>2012-04-23</t>
+  </si>
+  <si>
+    <t>081256467761</t>
+  </si>
+  <si>
+    <t>1000000030</t>
+  </si>
+  <si>
+    <t>3278720362327910</t>
+  </si>
+  <si>
+    <t>2012-09-11</t>
+  </si>
+  <si>
+    <t>081217513900</t>
   </si>
 </sst>
 </file>
@@ -730,44 +1183,44 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI31"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="37.705" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="26" max="26" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="28" max="28" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="29" max="29" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="30" max="30" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="31" max="31" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="32" max="32" width="43.561" bestFit="true" customWidth="true" style="0"/>
-    <col min="33" max="33" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="34" max="34" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="35" max="35" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.998" customWidth="true" style="0"/>
+    <col min="2" max="2" width="5.856" customWidth="true" style="0"/>
+    <col min="3" max="3" width="12.854" customWidth="true" style="0"/>
+    <col min="4" max="4" width="19.995" customWidth="true" style="0"/>
+    <col min="5" max="5" width="22.28" customWidth="true" style="0"/>
+    <col min="6" max="6" width="17.567" customWidth="true" style="0"/>
+    <col min="7" max="7" width="16.425" customWidth="true" style="0"/>
+    <col min="8" max="8" width="19.995" customWidth="true" style="0"/>
+    <col min="9" max="9" width="16.425" customWidth="true" style="0"/>
+    <col min="10" max="10" width="9.283" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18.71" customWidth="true" style="0"/>
+    <col min="12" max="12" width="26.993" customWidth="true" style="0"/>
+    <col min="13" max="13" width="23.423" customWidth="true" style="0"/>
+    <col min="14" max="14" width="25.851" customWidth="true" style="0"/>
+    <col min="15" max="15" width="22.28" customWidth="true" style="0"/>
+    <col min="16" max="16" width="13.997" customWidth="true" style="0"/>
+    <col min="17" max="17" width="15.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="17.567" customWidth="true" style="0"/>
+    <col min="19" max="19" width="25.851" customWidth="true" style="0"/>
+    <col min="20" max="20" width="26.993" customWidth="true" style="0"/>
+    <col min="21" max="21" width="16.425" customWidth="true" style="0"/>
+    <col min="22" max="22" width="23.423" customWidth="true" style="0"/>
+    <col min="23" max="23" width="26.993" customWidth="true" style="0"/>
+    <col min="24" max="24" width="37.705" customWidth="true" style="0"/>
+    <col min="25" max="25" width="11.711" customWidth="true" style="0"/>
+    <col min="26" max="26" width="29.421" customWidth="true" style="0"/>
+    <col min="27" max="27" width="17.567" customWidth="true" style="0"/>
+    <col min="28" max="28" width="10.569" customWidth="true" style="0"/>
+    <col min="29" max="29" width="28.136" customWidth="true" style="0"/>
+    <col min="30" max="30" width="19.995" customWidth="true" style="0"/>
+    <col min="31" max="31" width="11.711" customWidth="true" style="0"/>
+    <col min="32" max="32" width="43.561" customWidth="true" style="0"/>
+    <col min="33" max="33" width="29.421" customWidth="true" style="0"/>
+    <col min="34" max="34" width="17.567" customWidth="true" style="0"/>
+    <col min="35" max="35" width="26.993" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
@@ -887,91 +1340,81 @@
       <c r="C2" t="s">
         <v>35</v>
       </c>
-      <c r="D2">
-        <v>1234567890123456</v>
+      <c r="D2" t="s">
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
       <c r="O2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P2">
-        <v>45.5</v>
+        <v>42.4</v>
       </c>
       <c r="Q2">
-        <v>150.2</v>
+        <v>117</v>
       </c>
       <c r="R2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AB2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AC2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
+        <v>56</v>
+      </c>
       <c r="AI2">
         <v>1</v>
       </c>
@@ -984,93 +1427,83 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3">
-        <v>1234567890123457</v>
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P3">
-        <v>42.0</v>
+        <v>38.6</v>
       </c>
       <c r="Q3">
-        <v>148.5</v>
+        <v>116.3</v>
       </c>
       <c r="R3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="S3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="T3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AA3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD3" t="s">
         <v>68</v>
       </c>
-      <c r="AB3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE3"/>
-      <c r="AF3"/>
-      <c r="AG3"/>
-      <c r="AH3"/>
       <c r="AI3">
         <v>1</v>
       </c>
@@ -1083,100 +1516,82 @@
         <v>1003</v>
       </c>
       <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" t="s">
         <v>71</v>
       </c>
-      <c r="D4">
-        <v>1234567890123458</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>72</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
         <v>73</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="O4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4">
+        <v>47.7</v>
+      </c>
+      <c r="Q4">
+        <v>123.8</v>
+      </c>
+      <c r="R4" t="s">
         <v>74</v>
       </c>
-      <c r="H4" t="s">
+      <c r="S4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" t="s">
+        <v>46</v>
+      </c>
+      <c r="U4" t="s">
         <v>75</v>
       </c>
-      <c r="I4" t="s">
+      <c r="V4" t="s">
         <v>76</v>
       </c>
-      <c r="J4" t="s">
+      <c r="W4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X4" t="s">
         <v>77</v>
       </c>
-      <c r="K4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>43</v>
-      </c>
-      <c r="P4">
-        <v>40.5</v>
-      </c>
-      <c r="Q4">
-        <v>145.0</v>
-      </c>
-      <c r="R4" t="s">
+      <c r="Y4" t="s">
         <v>78</v>
       </c>
-      <c r="S4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T4" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="Z4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB4" t="s">
         <v>79</v>
       </c>
-      <c r="V4" t="s">
-        <v>80</v>
-      </c>
-      <c r="W4" t="s">
-        <v>81</v>
-      </c>
-      <c r="X4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>85</v>
-      </c>
       <c r="AC4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AD4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AI4">
         <v>1</v>
@@ -1190,93 +1605,83 @@
         <v>1004</v>
       </c>
       <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="O5" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5">
+        <v>51.5</v>
+      </c>
+      <c r="Q5">
+        <v>133</v>
+      </c>
+      <c r="R5" t="s">
+        <v>85</v>
+      </c>
+      <c r="S5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T5" t="s">
+        <v>46</v>
+      </c>
+      <c r="U5" t="s">
+        <v>86</v>
+      </c>
+      <c r="V5" t="s">
+        <v>87</v>
+      </c>
+      <c r="W5" t="s">
+        <v>49</v>
+      </c>
+      <c r="X5" t="s">
         <v>88</v>
       </c>
-      <c r="D5">
-        <v>1234567890123459</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="Y5" t="s">
         <v>89</v>
       </c>
-      <c r="F5" t="s">
+      <c r="Z5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB5" t="s">
         <v>90</v>
       </c>
-      <c r="G5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="AC5" t="s">
         <v>91</v>
       </c>
-      <c r="I5" t="s">
-        <v>92</v>
-      </c>
-      <c r="J5" t="s">
-        <v>93</v>
-      </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>94</v>
-      </c>
-      <c r="P5">
-        <v>48.0</v>
-      </c>
-      <c r="Q5">
-        <v>155.0</v>
-      </c>
-      <c r="R5" t="s">
-        <v>95</v>
-      </c>
-      <c r="S5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" t="s">
-        <v>96</v>
-      </c>
-      <c r="V5" t="s">
-        <v>97</v>
-      </c>
-      <c r="W5" t="s">
-        <v>48</v>
-      </c>
-      <c r="X5" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>67</v>
-      </c>
       <c r="AD5" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE5"/>
-      <c r="AF5"/>
-      <c r="AG5"/>
-      <c r="AH5"/>
+        <v>56</v>
+      </c>
       <c r="AI5">
         <v>1</v>
       </c>
@@ -1289,95 +1694,2289 @@
         <v>1005</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6">
-        <v>1234567890123460</v>
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J6" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="P6">
-        <v>50.0</v>
+        <v>52.1</v>
       </c>
       <c r="Q6">
-        <v>160.0</v>
+        <v>123.5</v>
       </c>
       <c r="R6" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="S6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T6" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="U6" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="V6" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="W6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X6" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="Y6" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="Z6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA6" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="AB6" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="AC6" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="AD6" t="s">
-        <v>119</v>
-      </c>
-      <c r="AE6"/>
-      <c r="AF6"/>
-      <c r="AG6"/>
-      <c r="AH6"/>
+        <v>68</v>
+      </c>
       <c r="AI6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1006</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="O7" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7">
+        <v>26.4</v>
+      </c>
+      <c r="Q7">
+        <v>126.7</v>
+      </c>
+      <c r="R7" t="s">
+        <v>85</v>
+      </c>
+      <c r="S7" t="s">
+        <v>46</v>
+      </c>
+      <c r="T7" t="s">
+        <v>46</v>
+      </c>
+      <c r="U7" t="s">
+        <v>103</v>
+      </c>
+      <c r="V7" t="s">
+        <v>104</v>
+      </c>
+      <c r="W7" t="s">
+        <v>49</v>
+      </c>
+      <c r="X7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1007</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="O8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P8">
+        <v>39.8</v>
+      </c>
+      <c r="Q8">
+        <v>142.6</v>
+      </c>
+      <c r="R8" t="s">
+        <v>85</v>
+      </c>
+      <c r="S8" t="s">
+        <v>46</v>
+      </c>
+      <c r="T8" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" t="s">
+        <v>112</v>
+      </c>
+      <c r="V8" t="s">
+        <v>113</v>
+      </c>
+      <c r="W8" t="s">
+        <v>49</v>
+      </c>
+      <c r="X8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1008</v>
+      </c>
+      <c r="C9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O9" t="s">
+        <v>44</v>
+      </c>
+      <c r="P9">
+        <v>48</v>
+      </c>
+      <c r="Q9">
+        <v>120.6</v>
+      </c>
+      <c r="R9" t="s">
+        <v>63</v>
+      </c>
+      <c r="S9" t="s">
+        <v>46</v>
+      </c>
+      <c r="T9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" t="s">
+        <v>119</v>
+      </c>
+      <c r="V9" t="s">
+        <v>113</v>
+      </c>
+      <c r="W9" t="s">
+        <v>49</v>
+      </c>
+      <c r="X9" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1009</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>44</v>
+      </c>
+      <c r="P10">
+        <v>24</v>
+      </c>
+      <c r="Q10">
+        <v>113</v>
+      </c>
+      <c r="R10" t="s">
+        <v>45</v>
+      </c>
+      <c r="S10" t="s">
+        <v>46</v>
+      </c>
+      <c r="T10" t="s">
+        <v>46</v>
+      </c>
+      <c r="U10" t="s">
+        <v>125</v>
+      </c>
+      <c r="V10" t="s">
+        <v>126</v>
+      </c>
+      <c r="W10" t="s">
+        <v>49</v>
+      </c>
+      <c r="X10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1010</v>
+      </c>
+      <c r="C11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
+        <v>131</v>
+      </c>
+      <c r="J11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" t="s">
+        <v>43</v>
+      </c>
+      <c r="O11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P11">
+        <v>59.6</v>
+      </c>
+      <c r="Q11">
+        <v>130.6</v>
+      </c>
+      <c r="R11" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" t="s">
+        <v>46</v>
+      </c>
+      <c r="T11" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" t="s">
+        <v>132</v>
+      </c>
+      <c r="V11" t="s">
+        <v>133</v>
+      </c>
+      <c r="W11" t="s">
+        <v>49</v>
+      </c>
+      <c r="X11" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1011</v>
+      </c>
+      <c r="C12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" t="s">
+        <v>139</v>
+      </c>
+      <c r="J12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12">
+        <v>3</v>
+      </c>
+      <c r="O12" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12">
+        <v>53.9</v>
+      </c>
+      <c r="Q12">
+        <v>123.6</v>
+      </c>
+      <c r="R12" t="s">
+        <v>85</v>
+      </c>
+      <c r="S12" t="s">
+        <v>46</v>
+      </c>
+      <c r="T12" t="s">
+        <v>46</v>
+      </c>
+      <c r="U12" t="s">
+        <v>140</v>
+      </c>
+      <c r="V12" t="s">
+        <v>141</v>
+      </c>
+      <c r="W12" t="s">
+        <v>49</v>
+      </c>
+      <c r="X12" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1012</v>
+      </c>
+      <c r="C13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" t="s">
+        <v>146</v>
+      </c>
+      <c r="J13" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O13" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13">
+        <v>33.3</v>
+      </c>
+      <c r="Q13">
+        <v>122.3</v>
+      </c>
+      <c r="R13" t="s">
+        <v>85</v>
+      </c>
+      <c r="S13" t="s">
+        <v>46</v>
+      </c>
+      <c r="T13" t="s">
+        <v>46</v>
+      </c>
+      <c r="U13" t="s">
+        <v>147</v>
+      </c>
+      <c r="V13" t="s">
+        <v>148</v>
+      </c>
+      <c r="W13" t="s">
+        <v>49</v>
+      </c>
+      <c r="X13" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>154</v>
+      </c>
+      <c r="J14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" t="s">
+        <v>43</v>
+      </c>
+      <c r="O14" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14">
+        <v>59.1</v>
+      </c>
+      <c r="Q14">
+        <v>151.9</v>
+      </c>
+      <c r="R14" t="s">
+        <v>85</v>
+      </c>
+      <c r="S14" t="s">
+        <v>46</v>
+      </c>
+      <c r="T14" t="s">
+        <v>46</v>
+      </c>
+      <c r="U14" t="s">
+        <v>155</v>
+      </c>
+      <c r="V14" t="s">
+        <v>133</v>
+      </c>
+      <c r="W14" t="s">
+        <v>49</v>
+      </c>
+      <c r="X14" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1014</v>
+      </c>
+      <c r="C15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" t="s">
+        <v>138</v>
+      </c>
+      <c r="G15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15" t="s">
+        <v>43</v>
+      </c>
+      <c r="O15" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15">
+        <v>60.2</v>
+      </c>
+      <c r="Q15">
+        <v>149.6</v>
+      </c>
+      <c r="R15" t="s">
+        <v>74</v>
+      </c>
+      <c r="S15" t="s">
+        <v>46</v>
+      </c>
+      <c r="T15" t="s">
+        <v>46</v>
+      </c>
+      <c r="U15" t="s">
+        <v>161</v>
+      </c>
+      <c r="V15" t="s">
+        <v>162</v>
+      </c>
+      <c r="W15" t="s">
+        <v>49</v>
+      </c>
+      <c r="X15" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>1015</v>
+      </c>
+      <c r="C16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" t="s">
+        <v>167</v>
+      </c>
+      <c r="J16" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" t="s">
+        <v>43</v>
+      </c>
+      <c r="O16" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16">
+        <v>57.2</v>
+      </c>
+      <c r="Q16">
+        <v>132.4</v>
+      </c>
+      <c r="R16" t="s">
+        <v>63</v>
+      </c>
+      <c r="S16" t="s">
+        <v>46</v>
+      </c>
+      <c r="T16" t="s">
+        <v>46</v>
+      </c>
+      <c r="U16" t="s">
+        <v>168</v>
+      </c>
+      <c r="V16" t="s">
+        <v>141</v>
+      </c>
+      <c r="W16" t="s">
+        <v>49</v>
+      </c>
+      <c r="X16" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>1016</v>
+      </c>
+      <c r="C17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" t="s">
+        <v>175</v>
+      </c>
+      <c r="J17" t="s">
+        <v>176</v>
+      </c>
+      <c r="K17" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
+        <v>44</v>
+      </c>
+      <c r="P17">
+        <v>49.2</v>
+      </c>
+      <c r="Q17">
+        <v>146.9</v>
+      </c>
+      <c r="R17" t="s">
+        <v>63</v>
+      </c>
+      <c r="S17" t="s">
+        <v>46</v>
+      </c>
+      <c r="T17" t="s">
+        <v>46</v>
+      </c>
+      <c r="U17" t="s">
+        <v>177</v>
+      </c>
+      <c r="V17" t="s">
+        <v>178</v>
+      </c>
+      <c r="W17" t="s">
+        <v>49</v>
+      </c>
+      <c r="X17" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>1017</v>
+      </c>
+      <c r="C18" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E18" t="s">
+        <v>183</v>
+      </c>
+      <c r="F18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" t="s">
+        <v>184</v>
+      </c>
+      <c r="J18" t="s">
+        <v>185</v>
+      </c>
+      <c r="K18" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18">
+        <v>60.5</v>
+      </c>
+      <c r="Q18">
+        <v>124.6</v>
+      </c>
+      <c r="R18" t="s">
+        <v>45</v>
+      </c>
+      <c r="S18" t="s">
+        <v>46</v>
+      </c>
+      <c r="T18" t="s">
+        <v>46</v>
+      </c>
+      <c r="U18" t="s">
+        <v>186</v>
+      </c>
+      <c r="V18" t="s">
+        <v>187</v>
+      </c>
+      <c r="W18" t="s">
+        <v>49</v>
+      </c>
+      <c r="X18" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>1018</v>
+      </c>
+      <c r="C19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" t="s">
+        <v>191</v>
+      </c>
+      <c r="F19" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" t="s">
+        <v>192</v>
+      </c>
+      <c r="J19" t="s">
+        <v>193</v>
+      </c>
+      <c r="K19" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P19">
+        <v>51.3</v>
+      </c>
+      <c r="Q19">
+        <v>156</v>
+      </c>
+      <c r="R19" t="s">
+        <v>45</v>
+      </c>
+      <c r="S19" t="s">
+        <v>46</v>
+      </c>
+      <c r="T19" t="s">
+        <v>46</v>
+      </c>
+      <c r="U19" t="s">
+        <v>194</v>
+      </c>
+      <c r="V19" t="s">
+        <v>148</v>
+      </c>
+      <c r="W19" t="s">
+        <v>49</v>
+      </c>
+      <c r="X19" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>1019</v>
+      </c>
+      <c r="C20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" t="s">
+        <v>197</v>
+      </c>
+      <c r="E20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20" t="s">
+        <v>198</v>
+      </c>
+      <c r="J20" t="s">
+        <v>42</v>
+      </c>
+      <c r="K20" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="O20" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20">
+        <v>58.6</v>
+      </c>
+      <c r="Q20">
+        <v>126</v>
+      </c>
+      <c r="R20" t="s">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s">
+        <v>46</v>
+      </c>
+      <c r="T20" t="s">
+        <v>46</v>
+      </c>
+      <c r="U20" t="s">
+        <v>199</v>
+      </c>
+      <c r="V20" t="s">
+        <v>200</v>
+      </c>
+      <c r="W20" t="s">
+        <v>49</v>
+      </c>
+      <c r="X20" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>1020</v>
+      </c>
+      <c r="C21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" t="s">
+        <v>203</v>
+      </c>
+      <c r="F21" t="s">
+        <v>204</v>
+      </c>
+      <c r="G21" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" t="s">
+        <v>40</v>
+      </c>
+      <c r="I21" t="s">
+        <v>205</v>
+      </c>
+      <c r="J21" t="s">
+        <v>206</v>
+      </c>
+      <c r="K21" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
+      <c r="O21" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21">
+        <v>33.2</v>
+      </c>
+      <c r="Q21">
+        <v>146.8</v>
+      </c>
+      <c r="R21" t="s">
+        <v>85</v>
+      </c>
+      <c r="S21" t="s">
+        <v>46</v>
+      </c>
+      <c r="T21" t="s">
+        <v>46</v>
+      </c>
+      <c r="U21" t="s">
+        <v>207</v>
+      </c>
+      <c r="V21" t="s">
+        <v>208</v>
+      </c>
+      <c r="W21" t="s">
+        <v>49</v>
+      </c>
+      <c r="X21" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>1021</v>
+      </c>
+      <c r="C22" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22" t="s">
+        <v>210</v>
+      </c>
+      <c r="E22" t="s">
+        <v>211</v>
+      </c>
+      <c r="F22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" t="s">
+        <v>40</v>
+      </c>
+      <c r="I22" t="s">
+        <v>212</v>
+      </c>
+      <c r="J22" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22">
+        <v>3</v>
+      </c>
+      <c r="O22" t="s">
+        <v>44</v>
+      </c>
+      <c r="P22">
+        <v>55.9</v>
+      </c>
+      <c r="Q22">
+        <v>162.7</v>
+      </c>
+      <c r="R22" t="s">
+        <v>45</v>
+      </c>
+      <c r="S22" t="s">
+        <v>46</v>
+      </c>
+      <c r="T22" t="s">
+        <v>46</v>
+      </c>
+      <c r="U22" t="s">
+        <v>213</v>
+      </c>
+      <c r="V22" t="s">
+        <v>214</v>
+      </c>
+      <c r="W22" t="s">
+        <v>49</v>
+      </c>
+      <c r="X22" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>1022</v>
+      </c>
+      <c r="C23" t="s">
+        <v>215</v>
+      </c>
+      <c r="D23" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" t="s">
+        <v>109</v>
+      </c>
+      <c r="F23" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" t="s">
+        <v>40</v>
+      </c>
+      <c r="I23" t="s">
+        <v>217</v>
+      </c>
+      <c r="J23" t="s">
+        <v>193</v>
+      </c>
+      <c r="K23" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>44</v>
+      </c>
+      <c r="P23">
+        <v>67.3</v>
+      </c>
+      <c r="Q23">
+        <v>129</v>
+      </c>
+      <c r="R23" t="s">
+        <v>74</v>
+      </c>
+      <c r="S23" t="s">
+        <v>46</v>
+      </c>
+      <c r="T23" t="s">
+        <v>46</v>
+      </c>
+      <c r="U23" t="s">
+        <v>218</v>
+      </c>
+      <c r="V23" t="s">
+        <v>219</v>
+      </c>
+      <c r="W23" t="s">
+        <v>49</v>
+      </c>
+      <c r="X23" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>1023</v>
+      </c>
+      <c r="C24" t="s">
+        <v>220</v>
+      </c>
+      <c r="D24" t="s">
+        <v>221</v>
+      </c>
+      <c r="E24" t="s">
+        <v>222</v>
+      </c>
+      <c r="F24" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" t="s">
+        <v>40</v>
+      </c>
+      <c r="I24" t="s">
+        <v>224</v>
+      </c>
+      <c r="J24" t="s">
+        <v>206</v>
+      </c>
+      <c r="K24" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+      <c r="O24" t="s">
+        <v>44</v>
+      </c>
+      <c r="P24">
+        <v>38.8</v>
+      </c>
+      <c r="Q24">
+        <v>132.4</v>
+      </c>
+      <c r="R24" t="s">
+        <v>45</v>
+      </c>
+      <c r="S24" t="s">
+        <v>46</v>
+      </c>
+      <c r="T24" t="s">
+        <v>46</v>
+      </c>
+      <c r="U24" t="s">
+        <v>225</v>
+      </c>
+      <c r="V24" t="s">
+        <v>187</v>
+      </c>
+      <c r="W24" t="s">
+        <v>49</v>
+      </c>
+      <c r="X24" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>1024</v>
+      </c>
+      <c r="C25" t="s">
+        <v>226</v>
+      </c>
+      <c r="D25" t="s">
+        <v>227</v>
+      </c>
+      <c r="E25" t="s">
+        <v>228</v>
+      </c>
+      <c r="F25" t="s">
+        <v>204</v>
+      </c>
+      <c r="G25" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" t="s">
+        <v>229</v>
+      </c>
+      <c r="J25" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="O25" t="s">
+        <v>44</v>
+      </c>
+      <c r="P25">
+        <v>37.8</v>
+      </c>
+      <c r="Q25">
+        <v>147.3</v>
+      </c>
+      <c r="R25" t="s">
+        <v>74</v>
+      </c>
+      <c r="S25" t="s">
+        <v>46</v>
+      </c>
+      <c r="T25" t="s">
+        <v>46</v>
+      </c>
+      <c r="U25" t="s">
+        <v>230</v>
+      </c>
+      <c r="V25" t="s">
+        <v>231</v>
+      </c>
+      <c r="W25" t="s">
+        <v>49</v>
+      </c>
+      <c r="X25" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>1025</v>
+      </c>
+      <c r="C26" t="s">
+        <v>233</v>
+      </c>
+      <c r="D26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E26" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" t="s">
+        <v>236</v>
+      </c>
+      <c r="G26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" t="s">
+        <v>40</v>
+      </c>
+      <c r="I26" t="s">
+        <v>237</v>
+      </c>
+      <c r="J26" t="s">
+        <v>42</v>
+      </c>
+      <c r="K26" t="s">
+        <v>43</v>
+      </c>
+      <c r="O26" t="s">
+        <v>44</v>
+      </c>
+      <c r="P26">
+        <v>64</v>
+      </c>
+      <c r="Q26">
+        <v>156.3</v>
+      </c>
+      <c r="R26" t="s">
+        <v>45</v>
+      </c>
+      <c r="S26" t="s">
+        <v>46</v>
+      </c>
+      <c r="T26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U26" t="s">
+        <v>238</v>
+      </c>
+      <c r="V26" t="s">
+        <v>239</v>
+      </c>
+      <c r="W26" t="s">
+        <v>49</v>
+      </c>
+      <c r="X26" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>1026</v>
+      </c>
+      <c r="C27" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" t="s">
+        <v>242</v>
+      </c>
+      <c r="E27" t="s">
+        <v>203</v>
+      </c>
+      <c r="F27" t="s">
+        <v>204</v>
+      </c>
+      <c r="G27" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" t="s">
+        <v>40</v>
+      </c>
+      <c r="I27" t="s">
+        <v>243</v>
+      </c>
+      <c r="J27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="O27" t="s">
+        <v>44</v>
+      </c>
+      <c r="P27">
+        <v>43.9</v>
+      </c>
+      <c r="Q27">
+        <v>141.4</v>
+      </c>
+      <c r="R27" t="s">
+        <v>85</v>
+      </c>
+      <c r="S27" t="s">
+        <v>46</v>
+      </c>
+      <c r="T27" t="s">
+        <v>46</v>
+      </c>
+      <c r="U27" t="s">
+        <v>244</v>
+      </c>
+      <c r="V27" t="s">
+        <v>245</v>
+      </c>
+      <c r="W27" t="s">
+        <v>49</v>
+      </c>
+      <c r="X27" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>1027</v>
+      </c>
+      <c r="C28" t="s">
+        <v>246</v>
+      </c>
+      <c r="D28" t="s">
+        <v>247</v>
+      </c>
+      <c r="E28" t="s">
+        <v>248</v>
+      </c>
+      <c r="F28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" t="s">
+        <v>40</v>
+      </c>
+      <c r="I28" t="s">
+        <v>249</v>
+      </c>
+      <c r="J28" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28">
+        <v>3</v>
+      </c>
+      <c r="O28" t="s">
+        <v>44</v>
+      </c>
+      <c r="P28">
+        <v>49.2</v>
+      </c>
+      <c r="Q28">
+        <v>139.2</v>
+      </c>
+      <c r="R28" t="s">
+        <v>74</v>
+      </c>
+      <c r="S28" t="s">
+        <v>46</v>
+      </c>
+      <c r="T28" t="s">
+        <v>46</v>
+      </c>
+      <c r="U28" t="s">
+        <v>250</v>
+      </c>
+      <c r="V28" t="s">
+        <v>251</v>
+      </c>
+      <c r="W28" t="s">
+        <v>49</v>
+      </c>
+      <c r="X28" t="s">
+        <v>252</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>1028</v>
+      </c>
+      <c r="C29" t="s">
+        <v>254</v>
+      </c>
+      <c r="D29" t="s">
+        <v>255</v>
+      </c>
+      <c r="E29" t="s">
+        <v>256</v>
+      </c>
+      <c r="F29" t="s">
+        <v>257</v>
+      </c>
+      <c r="G29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29" t="s">
+        <v>40</v>
+      </c>
+      <c r="I29" t="s">
+        <v>258</v>
+      </c>
+      <c r="J29" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="O29" t="s">
+        <v>44</v>
+      </c>
+      <c r="P29">
+        <v>56.1</v>
+      </c>
+      <c r="Q29">
+        <v>169.7</v>
+      </c>
+      <c r="R29" t="s">
+        <v>45</v>
+      </c>
+      <c r="S29" t="s">
+        <v>46</v>
+      </c>
+      <c r="T29" t="s">
+        <v>46</v>
+      </c>
+      <c r="U29" t="s">
+        <v>259</v>
+      </c>
+      <c r="V29" t="s">
+        <v>260</v>
+      </c>
+      <c r="W29" t="s">
+        <v>49</v>
+      </c>
+      <c r="X29" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>1029</v>
+      </c>
+      <c r="C30" t="s">
+        <v>262</v>
+      </c>
+      <c r="D30" t="s">
+        <v>263</v>
+      </c>
+      <c r="E30" t="s">
+        <v>264</v>
+      </c>
+      <c r="F30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G30" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30" t="s">
+        <v>265</v>
+      </c>
+      <c r="J30" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
+        <v>44</v>
+      </c>
+      <c r="P30">
+        <v>41</v>
+      </c>
+      <c r="Q30">
+        <v>149.6</v>
+      </c>
+      <c r="R30" t="s">
+        <v>63</v>
+      </c>
+      <c r="S30" t="s">
+        <v>46</v>
+      </c>
+      <c r="T30" t="s">
+        <v>46</v>
+      </c>
+      <c r="U30" t="s">
+        <v>266</v>
+      </c>
+      <c r="V30" t="s">
+        <v>65</v>
+      </c>
+      <c r="W30" t="s">
+        <v>49</v>
+      </c>
+      <c r="X30" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>1030</v>
+      </c>
+      <c r="C31" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" t="s">
+        <v>268</v>
+      </c>
+      <c r="E31" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" t="s">
+        <v>40</v>
+      </c>
+      <c r="I31" t="s">
+        <v>269</v>
+      </c>
+      <c r="J31" t="s">
+        <v>42</v>
+      </c>
+      <c r="K31" t="s">
+        <v>43</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="O31" t="s">
+        <v>44</v>
+      </c>
+      <c r="P31">
+        <v>53.9</v>
+      </c>
+      <c r="Q31">
+        <v>155.7</v>
+      </c>
+      <c r="R31" t="s">
+        <v>85</v>
+      </c>
+      <c r="S31" t="s">
+        <v>46</v>
+      </c>
+      <c r="T31" t="s">
+        <v>46</v>
+      </c>
+      <c r="U31" t="s">
+        <v>270</v>
+      </c>
+      <c r="V31" t="s">
+        <v>200</v>
+      </c>
+      <c r="W31" t="s">
+        <v>49</v>
+      </c>
+      <c r="X31" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI31">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
